--- a/www/download/IND.emp.s.un.WIOD16.xlsx
+++ b/www/download/IND.emp.s.un.WIOD16.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.045</t>
+          <t>9044700</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9.183</t>
+          <t>9182650</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9430010</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9.582</t>
+          <t>9581592</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9.904</t>
+          <t>9903713</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10.146</t>
+          <t>10145585</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10.467</t>
+          <t>10466510</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>10.752</t>
+          <t>10752408</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>10.866</t>
+          <t>10865505</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11.025</t>
+          <t>11024775</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.272</t>
+          <t>11271706</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>11.473</t>
+          <t>11472686</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11.558</t>
+          <t>11557676</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>11.622</t>
+          <t>11621580</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>11.863</t>
+          <t>11863007</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.756</t>
+          <t>3756460</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.783</t>
+          <t>3783490</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3779940</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.805</t>
+          <t>3804560</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.828</t>
+          <t>3828330</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3.874</t>
+          <t>3873820</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.941</t>
+          <t>3941430</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4.014</t>
+          <t>4013690</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4090350</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4.073</t>
+          <t>4072620</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4.102</t>
+          <t>4102240</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>4.166</t>
+          <t>4166000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.211</t>
+          <t>4211030</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4.231</t>
+          <t>4230600</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>4268490</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>4108800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>4165200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.157</t>
+          <t>4157500</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4.154</t>
+          <t>4154000</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4.194</t>
+          <t>4194500</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>4255500</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4.303</t>
+          <t>4302900</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>4.374</t>
+          <t>4373900</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>4.453</t>
+          <t>4453300</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4.446</t>
+          <t>4445500</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>4.474</t>
+          <t>4474000</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4.536</t>
+          <t>4535800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4.552</t>
+          <t>4551500</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>4.534</t>
+          <t>4534100</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4549800</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.319</t>
+          <t>3319350</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3309510</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.312</t>
+          <t>3312160</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.403</t>
+          <t>3402680</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.485</t>
+          <t>3484980</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.565</t>
+          <t>3564530</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.703</t>
+          <t>3702580</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.824</t>
+          <t>3823620</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.916</t>
+          <t>3915630</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3859510</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3.681</t>
+          <t>3680590</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3.585</t>
+          <t>3585490</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.474</t>
+          <t>3474040</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3470070</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3600340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>81.003</t>
+          <t>81003280</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81869941</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>85.429</t>
+          <t>85428531</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>86.351</t>
+          <t>86351144</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.884</t>
+          <t>90883574</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>94.081</t>
+          <t>94080942</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>95.555</t>
+          <t>95555438</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>97.564</t>
+          <t>97563631</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>99.374</t>
+          <t>99373771</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>99.518</t>
+          <t>99517771</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>99.173</t>
+          <t>99173384</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>100.261</t>
+          <t>100260574</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>101.492</t>
+          <t>101491931</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>102.993</t>
+          <t>102993067</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>104.031</t>
+          <t>104031462</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.143</t>
+          <t>15143131</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15.303</t>
+          <t>15302796</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.686</t>
+          <t>15686348</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16.037</t>
+          <t>16036946</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16.287</t>
+          <t>16287254</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16.535</t>
+          <t>16534560</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16.814</t>
+          <t>16814489</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17.224</t>
+          <t>17223936</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17.704</t>
+          <t>17704097</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>16.889</t>
+          <t>16889310</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>17.211</t>
+          <t>17210866</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>17.377</t>
+          <t>17377209</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>17.555</t>
+          <t>17555443</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>17.773</t>
+          <t>17772837</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18449875</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>719.604</t>
+          <t>719604312</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>728.107</t>
+          <t>728107454</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>737.284</t>
+          <t>737283544</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>744.531</t>
+          <t>744531055</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>752.281</t>
+          <t>752280978</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>759.77</t>
+          <t>759769706</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>765.353</t>
+          <t>765353192</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>770.887</t>
+          <t>770887157</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>777.013</t>
+          <t>777013044</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>784.924</t>
+          <t>784923939</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>784.663</t>
+          <t>784662540</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>840.443</t>
+          <t>840443021</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>854.216</t>
+          <t>854216282</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>857.826</t>
+          <t>857825563</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>858.367</t>
+          <t>858367350</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>316400</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>323510</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>330460</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>342550</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356140</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368510</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>375380</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>388690</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>396310</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394460</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>401280</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>403460</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>388970</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>365010</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>357510</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.859</t>
+          <t>4859390</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.846</t>
+          <t>4846400</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.877</t>
+          <t>4876770</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.838</t>
+          <t>4838090</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4.829</t>
+          <t>4828910</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.923</t>
+          <t>4922670</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.989</t>
+          <t>4988980</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>5.093</t>
+          <t>5093160</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5.204</t>
+          <t>5204090</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5110140</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>5.057</t>
+          <t>5057260</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>5.043</t>
+          <t>5043460</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5.065</t>
+          <t>5064670</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>5.081</t>
+          <t>5081060</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>5.109</t>
+          <t>5109230</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>39.917</t>
+          <t>39917000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>39.809</t>
+          <t>39809000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>39630000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39200000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>39.337</t>
+          <t>39337000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>39.326</t>
+          <t>39326000</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>39.635</t>
+          <t>39635000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>40.325</t>
+          <t>40325000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>40.856</t>
+          <t>40856000</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>40.892</t>
+          <t>40892000</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>41020000</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>41.577</t>
+          <t>41577000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42060000</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>42.328</t>
+          <t>42328000</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>42.706</t>
+          <t>42706000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.736</t>
+          <t>2736000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.754</t>
+          <t>2754000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.754</t>
+          <t>2754000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.735</t>
+          <t>2735000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>2712000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>2756000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.816</t>
+          <t>2816000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.877</t>
+          <t>2877000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.911</t>
+          <t>2911000</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.825</t>
+          <t>2825000</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.759</t>
+          <t>2759000</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2.757</t>
+          <t>2757000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>2741000</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2.745</t>
+          <t>2745000</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.765</t>
+          <t>2765000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>16.691</t>
+          <t>16691000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.248</t>
+          <t>17247800</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17.693</t>
+          <t>17692900</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18.282</t>
+          <t>18281800</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18970100</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19.784</t>
+          <t>19784000</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>20.609</t>
+          <t>20609200</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21.285</t>
+          <t>21284900</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>21.324</t>
+          <t>21324100</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>19.987</t>
+          <t>19986800</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19639500</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>19.113</t>
+          <t>19112500</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>18.338</t>
+          <t>18337700</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>17.798</t>
+          <t>17798300</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>17.965</t>
+          <t>17964500</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>589400</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>592200</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>589200</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>603800</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>617800</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>646800</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>648800</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>646400</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>582800</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>551800</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>589300</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>619200</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.298</t>
+          <t>2298300</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.332</t>
+          <t>2331600</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>2356900</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2360200</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>2373600</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.411</t>
+          <t>2410600</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.455</t>
+          <t>2454600</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.507</t>
+          <t>2506900</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.563</t>
+          <t>2562700</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.501</t>
+          <t>2501000</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.484</t>
+          <t>2483800</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2.515</t>
+          <t>2515500</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.538</t>
+          <t>2537600</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2519600</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.498</t>
+          <t>2498500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25.672</t>
+          <t>25672000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>26.041</t>
+          <t>26041000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26.161</t>
+          <t>26161000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>26.164</t>
+          <t>26164000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26.192</t>
+          <t>26192000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>26.376</t>
+          <t>26376000</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>26.667</t>
+          <t>26667000</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>27.042</t>
+          <t>27042000</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>27.167</t>
+          <t>27167000</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>26.861</t>
+          <t>26861000</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>26.892</t>
+          <t>26892000</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>27.107</t>
+          <t>27107000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>27.197</t>
+          <t>27197000</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>27.197</t>
+          <t>27197000</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>27.295</t>
+          <t>27295000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>27.482</t>
+          <t>27482000</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27.711</t>
+          <t>27711000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>27.944</t>
+          <t>27944000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28.225</t>
+          <t>28225000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>28530000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>28.852</t>
+          <t>28852000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29140000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>29.373</t>
+          <t>29373000</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>29.629</t>
+          <t>29629000</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>29.152</t>
+          <t>29152000</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>29.227</t>
+          <t>29227000</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>29.372</t>
+          <t>29372000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>29.693</t>
+          <t>29693000</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>30.044</t>
+          <t>30044000</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>30.726</t>
+          <t>30726000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.308</t>
+          <t>4308120</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.328</t>
+          <t>4328410</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4.434</t>
+          <t>4434300</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.496</t>
+          <t>4495720</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.604</t>
+          <t>4604100</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4.648</t>
+          <t>4648180</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.731</t>
+          <t>4731320</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4.795</t>
+          <t>4795150</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.856</t>
+          <t>4856400</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4.829</t>
+          <t>4829030</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4.706</t>
+          <t>4705510</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4.382</t>
+          <t>4381870</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.105</t>
+          <t>4105270</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3.957</t>
+          <t>3957320</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3.963</t>
+          <t>3962620</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.237</t>
+          <t>4237060</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4230330</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>4226960</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>4226950</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.186</t>
+          <t>4186440</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.174</t>
+          <t>4174190</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>4192230</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>4198060</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.116</t>
+          <t>4115520</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.013</t>
+          <t>4012990</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>4001580</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>4.003</t>
+          <t>4002760</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.008</t>
+          <t>4008240</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4.046</t>
+          <t>4045850</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>4.234</t>
+          <t>4233850</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>96.875</t>
+          <t>96874612</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>99.381</t>
+          <t>99380967</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>100.23</t>
+          <t>100229553</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>103.735</t>
+          <t>103734625</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>104.667</t>
+          <t>104667311</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>106.265</t>
+          <t>106264607</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>108.611</t>
+          <t>108611120</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>113.379</t>
+          <t>113378872</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>115.174</t>
+          <t>115174342</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>117.182</t>
+          <t>117182364</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>121.658</t>
+          <t>121658175</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>123.606</t>
+          <t>123605873</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>135.569</t>
+          <t>135569052</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>151.171</t>
+          <t>151171492</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>168.804</t>
+          <t>168803678</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>410.063</t>
+          <t>410063444</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>420.903</t>
+          <t>420902877</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>432.113</t>
+          <t>432113285</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>444.312</t>
+          <t>444312235</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>457.919</t>
+          <t>457919360</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>460.24</t>
+          <t>460240170</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>459.57</t>
+          <t>459570160</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>459.864</t>
+          <t>459864020</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>460.178</t>
+          <t>460178296</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>461.62</t>
+          <t>461620466</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>466.169</t>
+          <t>466169307</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>473.775</t>
+          <t>473774818</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>540.263</t>
+          <t>540263370</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>609.186</t>
+          <t>609186497</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>658.776</t>
+          <t>658776148</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>1711750</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1763360</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.792</t>
+          <t>1791710</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1825530</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.888</t>
+          <t>1888370</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.979</t>
+          <t>1978540</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2.071</t>
+          <t>2071140</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2.163</t>
+          <t>2162960</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.147</t>
+          <t>2146800</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>1971040</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.885</t>
+          <t>1884660</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1.849</t>
+          <t>1849420</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.839</t>
+          <t>1838510</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>1882080</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1.914</t>
+          <t>1914310</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23.021</t>
+          <t>23021300</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>23.473</t>
+          <t>23473300</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23.867</t>
+          <t>23867400</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24.218</t>
+          <t>24217900</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24.365</t>
+          <t>24364600</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>24.501</t>
+          <t>24501300</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>24.984</t>
+          <t>24983800</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>25.295</t>
+          <t>25294900</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>25.349</t>
+          <t>25349200</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>24.926</t>
+          <t>24925500</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>24.766</t>
+          <t>24765700</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>24.843</t>
+          <t>24842700</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>24.765</t>
+          <t>24764800</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>24.323</t>
+          <t>24322900</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>24.368</t>
+          <t>24368300</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>65.252</t>
+          <t>65252322.7551</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>64.76</t>
+          <t>64760027.9653</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>63.747</t>
+          <t>63747497.4753</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>63.536</t>
+          <t>63536206.7754</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>63.676</t>
+          <t>63676059.1939</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>63.916</t>
+          <t>63916437.3277</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>64.198</t>
+          <t>64197683.9437</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>64.438</t>
+          <t>64437719.7542</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>64.21</t>
+          <t>64209601.8889</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>63.274</t>
+          <t>63274319.8792</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>62.989</t>
+          <t>62988851.8943</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>62.858</t>
+          <t>62858109.5183</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>62.498</t>
+          <t>62497588.1091</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>62.041</t>
+          <t>62041289.9363</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>61.234</t>
+          <t>61233873.6916</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18.208</t>
+          <t>18207712</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18.649</t>
+          <t>18648512</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>19.309</t>
+          <t>19308557</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19.547</t>
+          <t>19546847</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>20.066</t>
+          <t>20066114</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>20.445</t>
+          <t>20445114</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>20.842</t>
+          <t>20841514</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>21.159</t>
+          <t>21158798</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>21.373</t>
+          <t>21373015</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21650268</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>21.925</t>
+          <t>21925244</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>22.849</t>
+          <t>22849294</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23809716</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24.059</t>
+          <t>24058954</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>24.449</t>
+          <t>24449000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1398990</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.346</t>
+          <t>1346080</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1397330</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.427</t>
+          <t>1427230</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.411</t>
+          <t>1411120</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.418</t>
+          <t>1417790</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>1416170</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.446</t>
+          <t>1445550</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1425080</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1317740</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1245360</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>1251970</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1273730</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.292</t>
+          <t>1292100</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1316640</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>262640</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279180</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>287460</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292900</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299650</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>307790</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319590</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>333700</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>349590</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353120</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>359550</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>370220</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>379120</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389880</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>405010</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>924250</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>942390</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>957440</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>966450</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>970300</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>976520</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1035070</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1068740</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1056780</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>900810</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>835520</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>847670</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>874810</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>891520</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>898030</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>31.748</t>
+          <t>31748216</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>31.448</t>
+          <t>31448123</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>31.609</t>
+          <t>31608837</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>33.468</t>
+          <t>33467686</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>34.829</t>
+          <t>34828912</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>35.203</t>
+          <t>35203494</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>36.683</t>
+          <t>36683335</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>37.417</t>
+          <t>37417215</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>37.982</t>
+          <t>37982023</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>36.633</t>
+          <t>36633161</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>37.267</t>
+          <t>37267340</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>37.792</t>
+          <t>37792488</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>38.861</t>
+          <t>38860525</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>38.612</t>
+          <t>38612134</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>38.997</t>
+          <t>38996763</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151000</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150670</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152460</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152830</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151040</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154210</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153870</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158670</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167640</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167800</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176090</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177180</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178840</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182720</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>193600</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8.207</t>
+          <t>8207000</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8.364</t>
+          <t>8364000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8.425</t>
+          <t>8425000</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8.376</t>
+          <t>8376000</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8.273</t>
+          <t>8273000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>8.328</t>
+          <t>8328000</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>8510000</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>8.758</t>
+          <t>8758000</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>8.907</t>
+          <t>8907000</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>8.824</t>
+          <t>8824000</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>8.768</t>
+          <t>8768000</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>8.843</t>
+          <t>8843000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>8.827</t>
+          <t>8827000</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>8.744</t>
+          <t>8744000</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>8.727</t>
+          <t>8727000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.777</t>
+          <t>14777000</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14.689</t>
+          <t>14689200</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>13.885</t>
+          <t>13885200</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13.606</t>
+          <t>13606100</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>13760300</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14.057</t>
+          <t>14057000</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>14.504</t>
+          <t>14503900</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>15.156</t>
+          <t>15155900</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>15.732</t>
+          <t>15731900</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>15789400</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>15370300</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>15.457</t>
+          <t>15457300</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15.475</t>
+          <t>15474900</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>15.464</t>
+          <t>15463500</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>15.572</t>
+          <t>15572100</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5.042</t>
+          <t>5041900</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5130150</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5149980</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5100210</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5.064</t>
+          <t>5064230</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5.041</t>
+          <t>5040940</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5.061</t>
+          <t>5060950</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>5.062</t>
+          <t>5061660</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5080130</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4.942</t>
+          <t>4941690</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>4.871</t>
+          <t>4871370</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>4.777</t>
+          <t>4776780</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>4.581</t>
+          <t>4581440</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4450200</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>4.545</t>
+          <t>4545450</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10.706</t>
+          <t>10706500</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10630300</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>9.568</t>
+          <t>9568400</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>9.569</t>
+          <t>9569100</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>9.411</t>
+          <t>9410900</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>9.266</t>
+          <t>9266100</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>9.319</t>
+          <t>9319500</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>9.366</t>
+          <t>9366100</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>9.349</t>
+          <t>9348800</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>9.186</t>
+          <t>9185600</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>9.134</t>
+          <t>9134200</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>9.073</t>
+          <t>9073000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>8.628</t>
+          <t>8627800</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>8.569</t>
+          <t>8569300</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>8.804</t>
+          <t>8803900</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>74.224</t>
+          <t>74224424</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>74.475</t>
+          <t>74474565</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>75.271</t>
+          <t>75270789</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>76.473</t>
+          <t>76472881</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>76.753</t>
+          <t>76753220</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>77330046</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>77.804</t>
+          <t>77804440</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>78.633</t>
+          <t>78632970</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>78.997</t>
+          <t>78997043</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>76.285</t>
+          <t>76285437</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>76.443</t>
+          <t>76443103</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>76.03</t>
+          <t>76029564</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>77.252</t>
+          <t>77251714</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>75.121</t>
+          <t>75120816</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>74.289</t>
+          <t>74288750</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>2013050</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2.036</t>
+          <t>2036100</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2040130</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.061</t>
+          <t>2061490</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.058</t>
+          <t>2057850</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2.085</t>
+          <t>2085230</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.131</t>
+          <t>2130930</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2.176</t>
+          <t>2176240</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>2248250</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2.203</t>
+          <t>2203170</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2169850</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>2208390</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2209520</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2.192</t>
+          <t>2192260</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2.223</t>
+          <t>2223140</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>905570</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>916260</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>937430</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>931720</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>934020</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>928730</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.944</t>
+          <t>944280</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>975770</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1000820</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>982920</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>962070</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>945990</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>937600</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>926990</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>940150</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>4301000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.396</t>
+          <t>4396000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4390000</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4.376</t>
+          <t>4376000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4.348</t>
+          <t>4348000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4.356</t>
+          <t>4356000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.434</t>
+          <t>4434000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4530000</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4.567</t>
+          <t>4567000</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4.462</t>
+          <t>4462000</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>4.506</t>
+          <t>4506000</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4.595</t>
+          <t>4595000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4.628</t>
+          <t>4628000</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4.672</t>
+          <t>4672000</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4750000</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>22.742</t>
+          <t>22741592</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>22.735</t>
+          <t>22734700</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21.819</t>
+          <t>21818750</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>21.461</t>
+          <t>21461235</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>22.014</t>
+          <t>22014471</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>22.154</t>
+          <t>22153910</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>21.265</t>
+          <t>21264783</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>20.927</t>
+          <t>20927003</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>21.405</t>
+          <t>21405044</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>21.593</t>
+          <t>21593295</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>22.863</t>
+          <t>22863011</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>24.299</t>
+          <t>24298768</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>26.486</t>
+          <t>26486468</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>28.879</t>
+          <t>28879456</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>32.329</t>
+          <t>32329192</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>16.928</t>
+          <t>16928066</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17.059</t>
+          <t>17059329</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>18.078</t>
+          <t>18077591</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18.115</t>
+          <t>18115492</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>18.342</t>
+          <t>18341731</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18.565</t>
+          <t>18564527</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>19.007</t>
+          <t>19007060</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>19.236</t>
+          <t>19236306</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>19.036</t>
+          <t>19036336</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19270147</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>19.723</t>
+          <t>19722896</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>19.581</t>
+          <t>19580746</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>19.902</t>
+          <t>19902102</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>20.227</t>
+          <t>20227155</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>20.207</t>
+          <t>20206844</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>150.433</t>
+          <t>150433351</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>150.399</t>
+          <t>150399160</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>149.192</t>
+          <t>149192148</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>148.589</t>
+          <t>148589267</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>150.048</t>
+          <t>150048193</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>151999622</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>155.009</t>
+          <t>155008647</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>155.569</t>
+          <t>155568502</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>154.696</t>
+          <t>154696176</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>147.906</t>
+          <t>147906284</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>146.533</t>
+          <t>146533434</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>147.899</t>
+          <t>147898641</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>150.631</t>
+          <t>150631025</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>152.958</t>
+          <t>152958083</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>155.77</t>
+          <t>155770460</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>947.617</t>
+          <t>947616738</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>974.461</t>
+          <t>974461081.4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1000.729</t>
+          <t>1000728599</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1033.017</t>
+          <t>1033016768</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1066.89</t>
+          <t>1066890156</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1091.838</t>
+          <t>1091838419</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1119.505</t>
+          <t>1119505492</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1147.144</t>
+          <t>1147144461</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1172.476</t>
+          <t>1172475726</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1193.77</t>
+          <t>1193770097</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1218.07</t>
+          <t>1218069956</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1281.007</t>
+          <t>1281007320</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1356.393</t>
+          <t>1356393463</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1428.937</t>
+          <t>1428936841</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1491.948</t>
+          <t>1491947563</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2880.537</t>
+          <t>2880537164.7551</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2932.349</t>
+          <t>2932348964.3653</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2983.112</t>
+          <t>2983112117.4753</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>3042.556</t>
+          <t>3042556467.7754</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>3109.826</t>
+          <t>3109826054.1939</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3156.019</t>
+          <t>3156018759.3277</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>3202.181</t>
+          <t>3202180879.9437</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>3250.085</t>
+          <t>3250084707.7542</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>3288.898</t>
+          <t>3288898356.8889</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3306.051</t>
+          <t>3306050917.8792</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>3338.984</t>
+          <t>3338984003.8943</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>3472.798</t>
+          <t>3472798072.5183</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>3649.263</t>
+          <t>3649263036.1091</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>3813.588</t>
+          <t>3813587645.9363</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>3954.229</t>
+          <t>3954229406.6916</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1597780</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1578210</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.603</t>
+          <t>1602830</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1609940</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.633</t>
+          <t>1633270</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1636890</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>1682730</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>1719450</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1779870</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1767540</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.696</t>
+          <t>1695650</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>1631720</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1571850</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1531350</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1570100</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.012</t>
+          <t>4012254</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4.118</t>
+          <t>4118131</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4.146</t>
+          <t>4146218</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>4134238</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>4165458</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>4.205</t>
+          <t>4204780</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>4.286</t>
+          <t>4285666</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>4.398</t>
+          <t>4398199</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>4.502</t>
+          <t>4501677</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4580104</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>4.683</t>
+          <t>4683310</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4890381</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4960441</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>5.022</t>
+          <t>5021571</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>5.085</t>
+          <t>5084671</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>2328000</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2330000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2.343</t>
+          <t>2343000</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.318</t>
+          <t>2318000</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.331</t>
+          <t>2331000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2.362</t>
+          <t>2362000</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2.442</t>
+          <t>2442000</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2.542</t>
+          <t>2542000</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>2626000</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.612</t>
+          <t>2612000</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2.601</t>
+          <t>2601000</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>2638000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.689</t>
+          <t>2689000</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2.727</t>
+          <t>2727000</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2.747</t>
+          <t>2747000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4687,12 +4692,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
